--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_01_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_01_19_Cau.xlsx
@@ -678,10 +678,24 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt thứ tự đọc theo cột và phần văn bản native.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt thứ tự đọc theo cột và phần văn bản native.</t>
+- [Xử lý riêng 3 vùng tài liệu] (1.5 điểm): Chọn đúng native text cho tiêu đề, table OCR cho bảng, và Multimodal VLM/Mermaid cho sơ đồ có mũi tên.
+- [Bản trích xuất cuối cùng] (1.5 điểm): Mô tả rõ định dạng Markdown cấu trúc phân cấp, bảng Markdown và đồ thị luồng quan hệ nhân quả.
+- [Không coi OCR là bằng chứng bố cục] (1.0 điểm): Khẳng định OCR thuần làm mất quan hệ mũi tên và yêu cầu cấu trúc hóa ngữ nghĩa thay vì phụ thuộc thứ tự quét.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn cách xử lý cho từng vùng tài liệu:
+- Vùng 1 (Tiêu đề chữ rõ ràng): Trích xuất văn bản số trực tiếp (Digital Native Text Extraction) bằng thư viện PDF parser (như PyPDF, PDFMiner, pypdfium2) để thu nhận chuỗi ký tự nguyên bản, nhanh và chính xác 100% không qua OCR.
+- Vùng 2 (Bảng biểu trong ảnh): Sử dụng mô hình Table OCR nhận biết cấu trúc (ví dụ: Azure Document Intelligence Layout API, Table Transformer, hoặc Camelot) để nhận diện ranh giới ô, cấu trúc hàng - cột, xuất ra bảng Markdown hoặc HTML `&lt;table&gt;` nhằm bảo toàn mối liên hệ dữ liệu.
+- Vùng 3 (Sơ đồ mà mũi tên quyết định ý nghĩa): Không dùng OCR thuần túy. Sử dụng Mô hình Đa phương thức (Multimodal Vision-Language Model như GPT-4o, Claude 3.5 Sonnet, hoặc Gemini 1.5 Pro) với prompt chuyên biệt: 'Phân tích sơ đồ quy trình, nhận diện các nút và chiều mũi tên chỉ luồng quyết định, xuất thành mã Mermaid graph hoặc luồng tuần tự dạng If-Then-Else'.
+2. Mô tả bản trích xuất cuối cùng để không coi OCR là bằng chứng bố cục:
+Bản trích xuất cuối cùng là một tài liệu Markdown có cấu trúc ngữ nghĩa (Semantic Markdown), trong đó:
+- Tiêu đề được định dạng bằng `#` hoặc `##`.
+- Bảng biểu được chuyển thành định dạng Markdown Table chuẩn.
+- Sơ đồ được diễn giải thành luồng văn bản tường minh có thứ tự logic và khối mã `mermaid` biểu diễn đồ thị directed graph.
+Các khối dữ liệu được phân định bằng nhãn cấu trúc rõ ràng, tuyệt đối không phụ thuộc vào thứ tự dòng quét ngẫu nhiên từ OCR.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+OCR truyền thống chỉ là bộ nhận diện ký tự quang học phẳng (Flat Character Recognizer), hoàn toàn mù đối với quan hệ không gian, thứ tự đọc hai cột, và ngữ nghĩa định hướng của mũi tên trong sơ đồ. Bộ trích xuất hiện đại phải là Layout-Aware &amp; Multimodal Pipeline: phân vùng tài liệu thành các khối (Text, Table, Diagram) và áp dụng công cụ chuyên dụng cho từng khối để bảo toàn trọn vẹn ngữ nghĩa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Unstructured.io Documentation: 'Layout-Aware Document Partitioning and Multimodal Processing' &amp; Microsoft Table-Transformer</t>
         </is>
       </c>
     </row>
@@ -766,10 +780,21 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt quan hệ giữa tiêu đề cột và giá trị, rồi kiểm tra đơn vị cùng ghi chú.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt quan hệ giữa tiêu đề cột và giá trị, rồi kiểm tra đơn vị cùng ghi chú.</t>
+- [Sửa liên kết dấu * chính xác] (1.5 điểm): Nêu rõ việc gỡ bỏ dấu * khỏi phòng Marketing và neo giữ đúng vào phòng Sales kèm giải nghĩa ngoại lệ.
+- [Kiểm tra quan hệ Tiêu đề &amp; Đơn vị %] (1.0 điểm): Kiểm tra tính nhất quán giữa đơn vị % ở header và các giá trị trong cột.
+- [Kiểm tra logic Hàng Tổng và Footnote Scope] (1.5 điểm): Kiểm tra tính toán hàng tổng chống row-shift và xác minh phạm vi áp dụng của ghi chú.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa chữa liên kết bị sai (Relational Association Repair):
+- Khắc phục lỗi rơi dấu `*`: Dấu `*` đại diện cho một ghi chú ngoại lệ (Footnote / Exception Rule). Trong bảng gốc, dấu `*` trỏ tới ngoại lệ chỉ áp dụng cho phòng Sales. Do OCR nhận diện sai vị trí làm rơi dấu sang hàng Marketing, hệ thống cần căn chỉnh lại tọa độ hình học (Bounding Box Alignment) hoặc sửa cấu trúc dữ liệu bảng: gỡ bỏ dấu `*` khỏi ô của phòng Marketing và gắn chính xác vào ô KPI tương ứng của phòng Sales.
+- Cấu trúc lại bảng: Gắn trực tiếp nội dung giải nghĩa của ghi chú chân trang `*` vào trường thuộc tính của phòng Sales: `"phòng_ban": "Sales", "kpi": "...", "ghi_chu_ngoai_le": "Ngoại lệ chỉ áp dụng cho phòng Sales"`.
+2. Các bước kiểm tra cần làm trước khi chọn cách biểu diễn lập chỉ mục (Pre-indexing Verification):
+- Kiểm tra 1 (Mối quan hệ Tiêu đề cột và Giá trị): Xác nhận mọi ô trong hàng đều ánh xạ đúng kiểu dữ liệu của tiêu đề cột (ví dụ cột có đơn vị `%` ở tiêu đề thì mọi giá trị bên dưới phải là tỷ lệ phần trăm hợp lệ từ 0 đến 100%).
+- Kiểm tra 2 (Toàn vẹn Hàng Tổng - Total Row Integrity): Kiểm tra logic tính toán: tổng các hàng phòng ban có khớp với Hàng Tổng hay không để phát hiện việc lệch hàng (Row Shift) do OCR.
+- Kiểm tra 3 (Tính cô lập của Ngoại lệ - Footnote Scoping): Đối chiếu văn bản ghi chú chân trang xem từ khóa của ghi chú (chỉ áp dụng Sales) có đồng nhất với vị trí neo dấu `*` đã sửa hay không.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong bảng biểu, dấu chú thích (Asterisk/Footnote) mang giá trị ngữ nghĩa điều kiện tối quan trọng. Nếu OCR làm trôi dạt dấu sao sang hàng khác, hệ thống RAG sẽ trả lời sai quy định cho cả hai phòng ban. Việc tiền kiểm tra quan hệ hàng-cột và kiểm chứng tính logic của hàng tổng là bước thẩm định bắt buộc trước khi đưa bảng vào chỉ mục vector.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Azure Document Intelligence Documentation: 'Table and Structure Extraction Best Practices' &amp; LlamaIndex Table Parser</t>
         </is>
       </c>
     </row>
@@ -848,10 +873,22 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt làm mới theo lô và đồng bộ phần thay đổi.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt làm mới theo lô và đồng bộ phần thay đổi.</t>
+- [Quy tắc bỏ qua dựa trên Content Hash] (1.5 điểm): Nêu rõ việc so sánh mã băm để bỏ qua 997 tệp không đổi, tránh re-indexing lãng phí.
+- [Cơ chế Atomic Upsert cho 3 tệp mới] (1.5 điểm): Mô tả việc xóa chunk cũ và nạp chunk mới nguyên tử kèm lưu checkpoint hội tụ.
+- [Chỉ rõ phần vòng đời độ mới tách biệt] (1.0 điểm): Nhận diện chính xác bài toán phát hiện tài liệu bị xóa nguồn (tombstone/deletion sync) là phần tách biệt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quy tắc khiến lần chạy lại hội tụ lũy thừa (Idempotent Delta Convergence Rules):
+- Quy tắc 1 (Content-Hash Based Skip): Với 997 tệp giữ nguyên mã băm SHA-256 (`hash_current == hash_recorded`), hệ thống lập tức bỏ qua (No-Op / Skip), không trích xuất và không re-embed lại.
+- Quy tắc 2 (Transactional Upsert &amp; Clean-up): Với 3 tệp có mã băm mới:
+  + Thao tác nguyên tử (Atomic Ingestion): Hệ thống xóa toàn bộ các chunk cũ của tài liệu qua lệnh `delete_by_doc_id(doc_id)` (hoặc sử dụng khóa ID đơn định `{doc_id}::{chunk_index}` với cơ chế overwrite).
+  + Nạp các chunk mới và ghi nhận trạng thái đã hoàn thành vào Bảng theo dõi trạng thái Ingestion (Checkpoint / State Store).
+- Tính hội tụ (Idempotency): Do mỗi tệp được xử lý độc lập và có trạng thái ghi nhận mã băm đã xử lý, khi tác vụ bị dừng lỗi và chạy lại từ đầu, hệ thống chỉ kiểm tra mã băm và tiếp tục xử lý những tệp chưa hoàn tất; kết quả cuối cùng của kho dữ liệu luôn đồng nhất dù chạy lại 1 lần hay 10 lần.
+2. Phần thuộc vòng đời độ mới chưa cần giải quyết trong câu này:
+- Vấn đề **Phát hiện và Xóa các tài liệu đã bị xóa khỏi hệ thống nguồn (Deletions / Tombstones / Pruning Lifecycle)**: Kịch bản trên chỉ đề cập đến việc đọc lại các tệp hiện có trong lô để cập nhật (Upsert/Skip). Quy trình đồng bộ các tệp bị xóa khỏi nguồn (Hard/Soft Deletes) thuộc về bài toán thu dọn rác (Garbage Collection / Tombstone Pruning) và sẽ được giải quyết ở quy trình riêng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tính lũy thừa (Idempotency) là thuộc tính sống còn của các đường ống nạp dữ liệu lớn (Big Data / RAG Ingestion). Khi có sự cố đứt gãy giữa chừng, hệ thống có thể chạy lại từ đầu mà không sinh ra dữ liệu trùng lặp (duplicate records) và không lãng phí chi phí tính toán cho các tệp không thay đổi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Databricks / Delta Lake Architecture: 'Idempotent Data Ingestion and Checkpointing' &amp; Pinecone Data Freshness Guide</t>
         </is>
       </c>
     </row>
@@ -930,10 +967,22 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định child chunk là đơn vị tìm kiếm và parent chunk là đơn vị được đưa vào context.
-Phân tích theo nguyên lý thiết kế: Xác định child chunk là đơn vị tìm kiếm và parent chunk là đơn vị được đưa vào context.</t>
+- [Đặc tả ID &amp; Quan hệ tham chiếu Parent-Child] (1.5 điểm): Thiết kế ID duy nhất gắn kèm version cho cả child và parent, có foreign key parent_id rõ ràng.
+- [Cơ chế truy xuất phân tầng] (1.0 điểm): Nêu rõ child chunk là đơn vị tìm kiếm vector và parent chunk là đơn vị đưa vào context.
+- [Thiết kế bộ lọc Metadata phiên bản] (1.5 điểm): Đưa ra bộ lọc bắt buộc is_active=true để loại bỏ triệt để child chunk phiên bản cũ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế định danh và ánh xạ Parent-Child (Identity &amp; Mapping Architecture):
+- Định danh Child Chunk (Search Unit): Khóa chính bao gồm thông tin phiên bản để phân biệt tuyệt đối: `child_id = "{doc_id}::{version}::child_{idx}"`.
+- Định danh Parent Chunk (Context Unit): `parent_id = "{doc_id}::{version}::parent_{idx}"`.
+- Trường ánh xạ (Explicit Foreign Key): Trong metadata của mỗi Child Chunk bắt buộc phải lưu trường tham chiếu `parent_id` trỏ chính xác về Parent Chunk của cùng phiên bản đó.
+- Quy trình truy xuất: Tìm kiếm vector được thực hiện trên các Child Chunks (đơn vị nhỏ, độ sắc nét ngữ nghĩa cao). Khi Child Chunk được chọn, hệ thống dùng `parent_id` để tra cứu trong Document Store và lấy Parent Chunk tương ứng (đơn vị lớn, ngữ cảnh đầy đủ) nạp vào prompt của LLM.
+2. Bộ lọc bắt buộc cần có (Mandatory Version Filter):
+- Bổ sung bộ lọc tiền truy vấn (Metadata Pre-filtering): `filter = {"is_active": true, "version": "current_active_version"}`.
+- Tác dụng: Ngăn chặn triệt để việc Child Chunk của phiên bản cũ lọt vào danh sách xếp hạng tìm kiếm, từ đó triệt tiêu hoàn toàn nguy cơ lấy nhầm Parent Chunk của chính sách đã hết hạn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiến trúc Parent-Child Retrieval tách rời đơn vị tìm kiếm (Child Chunk: 100-200 tokens) khỏi đơn vị tạo sinh (Parent Chunk: 500-1000 tokens). Để tránh nhầm lẫn giữa các phiên bản có câu chữ tương tự, khóa tham chiếu ngoại (parent_id) phải được định danh cùng không gian phiên bản và kết hợp chặt chẽ với bộ lọc hiệu lực (is_active filter).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'ParentDocumentRetriever' &amp; LlamaIndex 'RecursiveRetriever and Node References'</t>
         </is>
       </c>
     </row>
@@ -1016,10 +1065,22 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt chuỗi nguồn-tới-bản-ghi và candidate đã xếp hạng.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt chuỗi nguồn-tới-bản-ghi và candidate đã xếp hạng.</t>
+- [Xác định đúng tầng lỗi] (1.5 điểm): Chỉ ra lỗi ở bước Context Formatting tự ý đổi ID làm mất tính nhất quán giữa prompt và citation của model.
+- [Kế hoạch Logging 3 thời điểm then chốt] (1.5 điểm): Nêu rõ log tại thời điểm sau ranking (ranked candidates), sau formatting (formatted prompt &amp; ID map), và sau generation.
+- [Cơ chế Citation Validation] (1.0 điểm): Đề xuất bước kiểm tra tự động xem citation có thuộc tập ID hợp lệ trong context hay không.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định vị trí và nguyên nhân lỗi (Defect Localization):
+- Lỗi nằm ở **Tầng Định dạng Ngữ cảnh (Context Formatting / Packaging Layer)**, cụ thể là sự không nhất quán giữa cơ chế trích dẫn của mô hình và việc thay đổi định danh của bộ định dạng (ID Remapping Defect):
+  + Bộ định dạng đã tự ý đổi mã tài liệu gốc `doc-9` thành số thứ tự cục bộ (ví dụ: `[1]`, `[2]`, `[3]`).
+  + Tuy nhiên, LLM vẫn ghi nhớ hoặc bị lẫn với ID gốc `doc-9` (hoặc do trong prompt vẫn còn sót chuỗi `doc-9`), dẫn đến việc câu trả lời trích dẫn `doc-9` trong khi ngữ cảnh hiển thị chỉ có `doc-3`.
+2. Thành phần và Thời điểm cần ghi nhật ký để tái hiện và kiểm toán (Audit Logging Strategy):
+- Thời điểm 1 (Sau bước Retrieval / Reranking): Ghi log danh sách ứng viên đã xếp hạng: `ranked_candidates = [{rank: 1, doc_id: 'doc-9', score: 0.92}, {rank: 2, doc_id: 'doc-3', score: 0.88}]`.
+- Thời điểm 2 (Sau bước Context Formatting / Prompt Assembly): Ghi log nguyên văn chuỗi ngữ cảnh được tiêm vào LLM kèm bảng ánh xạ ID (ID Mapping Table): `formatted_context = "..."`, `id_map = {"[1]": "doc-9", "[2]": "doc-3"}`.
+- Thời điểm 3 (Sau bước Generation): Ghi log đầu ra thô của LLM và bước Citation Validator kiểm tra xem mọi ID trích dẫn có nằm trong tập ID được phép của `formatted_context` hay không.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống RAG phức tạp, sự trôi dạt định danh (ID Drift) giữa các tầng trung gian (Retrieval -&gt; Formatting -&gt; Prompt Injection -&gt; Generation) là nguyên nhân phổ biến gây lỗi trích dẫn ảo (Phantom Citation). Việc duy trì bảng ánh xạ tường minh và log đầy đủ các artifact trung gian là bắt buộc để đảm bảo khả năng tái hiện lỗi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+TruLens Documentation: 'Tracking Artifacts and Traceability in RAG Pipelines' &amp; LangSmith Observability Guide</t>
         </is>
       </c>
     </row>
@@ -1102,10 +1163,21 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt phân loại vùng và trích xuất native.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt phân loại vùng và trích xuất native.</t>
+- [Khẳng định không chỉ dùng native] (1.0 điểm): Bác bỏ việc chỉ dùng native extractor vì làm mất quan hệ nút-mũi tên.
+- [Thiết kế Fallback Multimodal VLM] (1.5 điểm): Đề xuất pipeline kết hợp ảnh crop sơ đồ và mô hình đa phương thức xuất ra định dạng Mermaid/Graph edges.
+- [Xác định rõ giới hạn kết luận] (1.5 điểm): Nêu rõ giới hạn áp dụng: chỉ định tuyến vùng sơ đồ sang VLM, giữ native text cho các đoạn văn thông thường để tối ưu chi phí/độ trễ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Có nên chỉ dùng bộ trích xuất native không?
+**KHÔNG.** Tuyệt đối không chỉ dùng bộ trích xuất native trong trường hợp này. Căn cứ: Trích xuất native chỉ đọc được các chuỗi ký tự rời rạc và trả về dạng danh sách tuyến tính phẳng, làm mất hoàn toàn quan hệ cấu trúc mạng: nút nguồn -&gt; nhãn mũi tên -&gt; nút đích. Đối với sơ đồ quy trình, mất quan hệ mũi tên đồng nghĩa với việc mất toàn bộ logic nghiệp vụ (thứ tự bước, điều kiện rẽ nhánh).
+2. Phương án dự phòng và quy trình định tuyến (Fallback &amp; Multimodal Pipeline):
+- Định tuyến thông minh: Khi bộ phát hiện vùng (Layout Detector) phân loại một khối là 'Diagram/Flowchart', hệ thống định tuyến khối này sang Bộ xử lý Thị giác - Đa phương thức (Multimodal VLM Pipeline như GPT-4o Vision hoặc Claude 3.5 Sonnet).
+- Kỹ thuật trích xuất: Cung cấp ảnh crop của sơ đồ kèm danh sách chữ native (làm gợi ý chống đọc sai chữ) và prompt: 'Trích xuất cấu trúc đồ thị luồng dưới dạng Mermaid flowchart hoặc danh sách các cạnh có hướng: Node A --[Điều kiện]--&gt; Node B'.
+3. Giới hạn của kết luận (Boundary of Conclusion):
+Kết luận này áp dụng cho các sơ đồ chứa quan hệ đồ thị/hình học; đối với các khối văn bản đoạn văn thông thường trên cùng trang tài liệu, bộ trích xuất native vẫn là lựa chọn số một về tốc độ và chi phí, không nên chuyển đổi toàn bộ trang sang VLM một cách lãng phí.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trích xuất văn bản từ sơ đồ là một tác vụ đa phương thức thực thụ: ý nghĩa không chỉ nằm ở ký tự mà nằm ở cấu trúc hình học và liên kết không gian (Spatial &amp; Graph Topology). Sự kết hợp giữa Text Extractor và Multimodal VLM là giải pháp tối ưu vừa đảm bảo độ chính xác ký tự vừa bảo toàn đồ thị quan hệ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Multimodal Parsing and Flowchart Extraction' &amp; Anthropic Vision Guides</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1256,22 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt ID nguồn ổn định và thao tác upsert.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt ID nguồn ổn định và thao tác upsert.</t>
+- [Bổ sung cơ chế đồng bộ xóa] (1.5 điểm): Thiết lập cơ chế xóa dựa trên sự kiện webhook hoặc vòng quét đối soát reconciliation loop để xóa triệt để chunk cũ.
+- [Phép kiểm tra phân biệt rạch ròi] (1.5 điểm): Tra cứu ID trong nguồn: nếu nguồn đã xóa mà index còn -&gt; lỗi Stale Index; nếu nguồn còn mà rank cao vô lý -&gt; lỗi Retrieval Ranking.
+- [Chính sách kiểm soát toàn vẹn] (1.0 điểm): Nhấn mạnh tầm quan trọng của việc dọn dẹp tombstone định kỳ để giữ index trong sạch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa chữa quy trình vòng đời đồng bộ (Freshness Lifecycle Repair):
+- Bổ sung cơ chế Đồng bộ xóa (Deletion / Tombstone Synchronization) vào tác vụ delta ingestion:
+  + Phương pháp 1 (Source Event/Webhook Triggered): Khi một tài liệu bị xóa ở hệ thống nguồn, nguồn phát sự kiện `DocumentDeleted(doc_id)`. Tác vụ delta nhận sự kiện và gọi ngay lệnh xóa triệt để: `vector_store.delete(filter={"doc_id": doc_id})`.
+  + Phương pháp 2 (Full Reconciliation Loop with Tombstones): Trong tác vụ batch định kỳ, lấy danh sách `active_doc_ids` từ hệ thống nguồn và so sánh với `indexed_doc_ids` trong Vector Store. Những ID tồn tại trong index nhưng không còn trong nguồn sẽ bị đưa vào danh sách xóa (Purge List) và thực hiện xóa hàng loạt.
+2. Phép kiểm phân biệt Bằng chứng cũ (Stale Evidence) với Lỗi xếp hạng ở Retrieval (Ranking Defect):
+- Kiểm tra trạng thái tồn tại của bản ghi trong nguồn (Source Existence Verification): Khi một chunk bị nghi ngờ xuất hiện trong kết quả search, thực hiện truy vấn trực tiếp vào Cơ sở dữ liệu nguồn bằng `doc_id` của chunk đó.
+  + Nếu bản ghi **không còn tồn tại trong nguồn** (đã bị xóa): Kết luận đây là **Lỗi độ tươi chỉ mục / Bằng chứng cũ (Stale Index / Deletion Lag Defect)**. Tầng retrieval không có lỗi vì nó chỉ tìm kiếm trên những gì đang có trong index.
+  + Nếu bản ghi **vẫn tồn tại trong nguồn** nhưng nội dung không liên quan mà vẫn đứng Top-1: Kết luận đây là **Lỗi xếp hạng truy xuất (Retrieval / Ranking Defect)**.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Vòng đời dữ liệu trong hệ thống RAG không chỉ có Insert và Update mà bắt buộc phải có Deletion Synchronization. Hiện tượng tài liệu 'ma' (Ghost Documents) vẫn xuất hiện sau khi đã bị xóa khỏi nguồn là lỗi nghiêm trọng về an toàn và bảo mật thông tin. Cần có phép kiểm tra phân định rõ giữa lỗi dữ liệu lỗi thời và lỗi thuật toán tìm kiếm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pinecone Learning Center: 'Managing Vector Deletions and Stale Data' &amp; Milvus Documentation: 'Delete Entities'</t>
         </is>
       </c>
     </row>
@@ -1266,10 +1350,24 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt bản ghi theo hàng và bản tóm tắt bảng.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt bản ghi theo hàng và bản tóm tắt bảng.</t>
+- [Biểu diễn chi tiết theo hàng] (1.5 điểm): Thiết kế biểu diễn từng hàng kết hợp tiêu đề cột để phục vụ truy vấn chi tiết.
+- [Biểu diễn tóm tắt toàn bảng] (1.5 điểm): Thiết kế biểu diễn tổng quan bảng Markdown kèm tóm tắt để phục vụ truy vấn khái quát.
+- [Thiết kế phép kiểm so sánh độ phủ] (1.0 điểm): Xây dựng testset chia 2 nhóm query và đo lường Fact Recall / Completeness.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế hai cách biểu diễn bảng dữ liệu (Two Table Representations):
+- **Biểu diễn 1: Bản ghi phân rã theo hàng (Row-level Structured Representation)**:
+  + Cấu trúc: Mỗi hàng trong bảng được tách thành một chunk độc lập, kết hợp tiêu đề cột và ngữ cảnh tên bảng. Ví dụ: `[Chính sách hoàn phí] - Điều kiện: Hủy trước 7 ngày | Mức phạt: 0% | Ngoại lệ: Áp dụng cho mọi học viên`.
+  + Mục đích: Phục vụ tối ưu cho các truy vấn điều kiện chi tiết, cụ thể của người dùng, giúp vector embedding có độ hội tụ ngữ nghĩa cao và khớp chính xác từng quy định nhỏ.
+- **Biểu diễn 2: Bản tóm tắt toàn bộ bảng (Table-level Summary / Full Table Markdown)**:
+  + Cấu trúc: Một chunk duy nhất chứa toàn bộ bảng Markdown kèm đoạn văn bản tóm tắt tổng quan: `Bảng quy định toàn diện về chính sách phạt hủy khóa học bao gồm 3 trường hợp: hủy sớm, hủy sát ngày và trường hợp bất khả kháng...`.
+  + Mục đích: Phục vụ cho các truy vấn mang tính khái quát, yêu cầu tóm tắt toàn bộ chính sách hoặc so sánh tổng thể các mức phạt.
+2. Thiết kế phép kiểm tra so sánh độ phủ (Coverage Comparison Test):
+- Xây dựng tập kiểm thử gồm 2 nhóm câu hỏi chuẩn: 10 câu hỏi tra cứu điều kiện chi tiết và 10 câu hỏi tóm tắt toàn bảng.
+- Đo lường chỉ số **Fact Recall / Context Completeness**: Kiểm tra xem câu trả lời được sinh ra có bao phủ đầy đủ tất cả các mức phạt và ngoại lệ hay không. Đánh giá tỷ lệ câu hỏi chi tiết tìm thấy đúng hàng tương ứng và tỷ lệ câu hỏi tổng quát bao phủ được toàn bộ bảng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bảng biểu vừa chứa dữ liệu chi tiết ở từng ô/hàng vừa chứa bức tranh tổng thể ở cấp độ bảng. Không có một dạng biểu diễn đơn lẻ nào phục vụ hoàn hảo cả hai loại câu hỏi này. Phương pháp Multi-Vector Representation (lưu đồng thời bản tóm tắt bảng và các hàng chi tiết có liên kết cha-con) là giải pháp chuẩn hóa cho dữ liệu bảng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Table Parsing and Multi-Vector Representation for Tables' &amp; LangChain Table Retrievers</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1452,26 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt sự mơ hồ/lệch từ vựng và điều phối theo bằng chứng.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt sự mơ hồ/lệch từ vựng và điều phối theo bằng chứng.</t>
+- [Thiết kế quy tắc Gating rõ ràng] (1.5 điểm): Xác định đúng điều kiện bypass (câu hỏi dài, rõ thực thể, độc lập) và điều kiện kích hoạt (câu hỏi ngắn, đa lượt, tham chiếu đại từ).
+- [Bảo toàn tên thực thể] (1.0 điểm): Nhấn mạnh cơ chế kiểm tra bảo toàn thực thể, chống rewrite làm sai lệch tên sản phẩm.
+- [Cơ chế Fallback &amp; Timeout] (1.5 điểm): Thiết lập timeout budget cho rewrite và fallback an toàn về query gốc khi gặp sự cố.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Quy tắc Kích hoạt có Điều kiện (Query Transformation Gating Rules):
+Tuyệt đối không chạy rewrite cho mọi query. Thiết lập một bộ kiểm soát cổng (Gating Classifier / Decision Tree) phân loại câu hỏi trước khi quyết định biến đổi:
+- **Điều kiện BỎ QUA Rewrite (Direct Retrieval Bypass)**:
+  + Câu hỏi có độ dài đủ lớn (ví dụ &gt;= 6 từ), chứa rõ ràng các thực thể xác định (Named Entities như tên sản phẩm cụ thể, mã lỗi chuẩn, thuật ngữ chuyên ngành).
+  + Câu hỏi độc lập không chứa đại từ thay thế mơ hồ (anaphora như 'nó', 'chính sách này', 'bước trên').
+  + Hành động: Bỏ qua rewrite, chuyển thẳng tới Direct Retrieval để bảo toàn SLA độ trễ (tiết kiệm 350 ms) và tránh làm sai lệch tên sản phẩm.
+- **Điều kiện KÍCH HOẠT Rewrite (Transform Trigger)**:
+  + Câu hỏi trong chuỗi hội thoại đa lượt có đại từ tham chiếu ('sản phẩm đó giá bao nhiêu?').
+  + Câu hỏi quá ngắn (&lt; 3 từ), mơ hồ hoặc có dấu hiệu sai lỗi chính tả nghiêm trọng.
+2. Cách xử lý khi lỗi và phương án dự phòng (Fallback &amp; Error Handling):
+- Giới hạn thời gian chờ (Timeout Budget): Áp dụng timeout nghiêm ngặt cho dịch vụ rewrite (ví dụ: `timeout = 250 ms`). Nếu rewrite bị timeout hoặc lỗi mạng, hệ thống lập tức fallback sử dụng câu hỏi gốc nguyên bản của người dùng.
+- Kiểm tra tính bảo toàn thực thể (Entity Preservation Check): So khớp thực thể trước và sau rewrite. Nếu phát hiện tên sản phẩm gốc bị biến đổi hoặc mất đi, hệ thống hủy kết quả rewrite và sử dụng query gốc.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Query Rewriting mang lại giá trị lớn cho các câu hỏi mơ hồ nhưng lại là gánh nặng độ trễ và rủi ro xuyên tạc thực thể (Entity Hallucination) đối với các câu hỏi đã rõ ràng. Việc thiết lập cổng kiểm soát (Gating) và cơ chế bảo toàn thực thể là nguyên tắc tối ưu hóa hiệu năng trong kiến trúc RAG.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Query Transformations and Fallback Routing' &amp; Cohere / LlamaIndex Query Rewriting Guides</t>
         </is>
       </c>
     </row>
